--- a/research/traditional_assets/database/data/slovenia/slovenia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0525</v>
+        <v>0.0272</v>
       </c>
       <c r="E2">
-        <v>0.0983</v>
+        <v>0.0634</v>
       </c>
       <c r="G2">
-        <v>0.08850537284272224</v>
+        <v>0.1499023851965028</v>
       </c>
       <c r="H2">
-        <v>0.08850537284272224</v>
+        <v>0.1499023851965028</v>
       </c>
       <c r="I2">
-        <v>0.09443178117876913</v>
+        <v>0.1101774042950514</v>
       </c>
       <c r="J2">
-        <v>0.07680181344796888</v>
+        <v>0.09330026852322497</v>
       </c>
       <c r="K2">
-        <v>113.6</v>
+        <v>108</v>
       </c>
       <c r="L2">
-        <v>0.07398241615109084</v>
+        <v>0.09167303284950344</v>
       </c>
       <c r="M2">
-        <v>44.7</v>
+        <v>82.5</v>
       </c>
       <c r="N2">
-        <v>0.04725658103393594</v>
+        <v>0.09851922617625986</v>
       </c>
       <c r="O2">
-        <v>0.3934859154929578</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="P2">
-        <v>44.7</v>
+        <v>82.5</v>
       </c>
       <c r="Q2">
-        <v>0.04725658103393594</v>
+        <v>0.09851922617625986</v>
       </c>
       <c r="R2">
-        <v>0.3934859154929578</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>114.4</v>
+        <v>117.4</v>
       </c>
       <c r="V2">
-        <v>0.1209430172322656</v>
+        <v>0.140195844279914</v>
       </c>
       <c r="W2">
-        <v>0.1150496252785092</v>
+        <v>0.1038062283737024</v>
       </c>
       <c r="X2">
-        <v>0.05451721832221438</v>
+        <v>0.0904165081449806</v>
       </c>
       <c r="Y2">
-        <v>0.06053240695629484</v>
+        <v>0.01338972022872181</v>
       </c>
       <c r="Z2">
-        <v>1.626244439737344</v>
+        <v>1.184734513274336</v>
       </c>
       <c r="AA2">
-        <v>0.1248985220815041</v>
+        <v>0.1105360482172278</v>
       </c>
       <c r="AB2">
-        <v>0.05267370474411807</v>
+        <v>0.08779430083044153</v>
       </c>
       <c r="AC2">
-        <v>0.07222481733738607</v>
+        <v>0.02274174738678625</v>
       </c>
       <c r="AD2">
-        <v>68.40000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>68.40000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="AG2">
-        <v>-46</v>
+        <v>-59.00000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.06743566992014198</v>
+        <v>0.06519312346505916</v>
       </c>
       <c r="AI2">
-        <v>0.06151632341037863</v>
+        <v>0.07625016320668494</v>
       </c>
       <c r="AJ2">
-        <v>-0.05111679075452828</v>
+        <v>-0.07579650565262078</v>
       </c>
       <c r="AK2">
-        <v>-0.04611528822055138</v>
+        <v>-0.0909791827293755</v>
       </c>
       <c r="AL2">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AM2">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AN2">
-        <v>0.4173276388041489</v>
+        <v>0.3847167325428195</v>
       </c>
       <c r="AO2">
-        <v>46.7741935483871</v>
+        <v>50.11583011583012</v>
       </c>
       <c r="AP2">
-        <v>-0.2806589383770592</v>
+        <v>-0.38866930171278</v>
       </c>
       <c r="AQ2">
-        <v>46.7741935483871</v>
+        <v>50.11583011583012</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0525</v>
+        <v>0.0272</v>
       </c>
       <c r="E3">
-        <v>0.0983</v>
+        <v>0.0634</v>
       </c>
       <c r="G3">
-        <v>0.08850537284272224</v>
+        <v>0.1499023851965028</v>
       </c>
       <c r="H3">
-        <v>0.08850537284272224</v>
+        <v>0.1499023851965028</v>
       </c>
       <c r="I3">
-        <v>0.09443178117876913</v>
+        <v>0.1101774042950514</v>
       </c>
       <c r="J3">
-        <v>0.07680181344796888</v>
+        <v>0.09330026852322497</v>
       </c>
       <c r="K3">
-        <v>113.6</v>
+        <v>108</v>
       </c>
       <c r="L3">
-        <v>0.07398241615109084</v>
+        <v>0.09167303284950344</v>
       </c>
       <c r="M3">
-        <v>44.7</v>
+        <v>82.5</v>
       </c>
       <c r="N3">
-        <v>0.04725658103393594</v>
+        <v>0.09851922617625986</v>
       </c>
       <c r="O3">
-        <v>0.3934859154929578</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="P3">
-        <v>44.7</v>
+        <v>82.5</v>
       </c>
       <c r="Q3">
-        <v>0.04725658103393594</v>
+        <v>0.09851922617625986</v>
       </c>
       <c r="R3">
-        <v>0.3934859154929578</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>114.4</v>
+        <v>117.4</v>
       </c>
       <c r="V3">
-        <v>0.1209430172322656</v>
+        <v>0.140195844279914</v>
       </c>
       <c r="W3">
-        <v>0.1150496252785092</v>
+        <v>0.1038062283737024</v>
       </c>
       <c r="X3">
-        <v>0.05451721832221438</v>
+        <v>0.0904165081449806</v>
       </c>
       <c r="Y3">
-        <v>0.06053240695629484</v>
+        <v>0.01338972022872181</v>
       </c>
       <c r="Z3">
-        <v>1.626244439737344</v>
+        <v>1.184734513274336</v>
       </c>
       <c r="AA3">
-        <v>0.1248985220815041</v>
+        <v>0.1105360482172278</v>
       </c>
       <c r="AB3">
-        <v>0.05267370474411807</v>
+        <v>0.08779430083044153</v>
       </c>
       <c r="AC3">
-        <v>0.07222481733738607</v>
+        <v>0.02274174738678625</v>
       </c>
       <c r="AD3">
-        <v>68.40000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>68.40000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="AG3">
-        <v>-46</v>
+        <v>-59.00000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.06743566992014198</v>
+        <v>0.06519312346505916</v>
       </c>
       <c r="AI3">
-        <v>0.06151632341037863</v>
+        <v>0.07625016320668494</v>
       </c>
       <c r="AJ3">
-        <v>-0.05111679075452828</v>
+        <v>-0.07579650565262078</v>
       </c>
       <c r="AK3">
-        <v>-0.04611528822055138</v>
+        <v>-0.0909791827293755</v>
       </c>
       <c r="AL3">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AM3">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AN3">
-        <v>0.4173276388041489</v>
+        <v>0.3847167325428195</v>
       </c>
       <c r="AO3">
-        <v>46.7741935483871</v>
+        <v>50.11583011583012</v>
       </c>
       <c r="AP3">
-        <v>-0.2806589383770592</v>
+        <v>-0.38866930171278</v>
       </c>
       <c r="AQ3">
-        <v>46.7741935483871</v>
+        <v>50.11583011583012</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/slovenia/slovenia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_insurance_general.xlsx
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0272</v>
+        <v>0.0405</v>
       </c>
       <c r="E2">
-        <v>0.0634</v>
+        <v>-0.0119</v>
       </c>
       <c r="G2">
-        <v>0.1499023851965028</v>
+        <v>0.1167169757079201</v>
       </c>
       <c r="H2">
-        <v>0.1499023851965028</v>
+        <v>0.1167169757079201</v>
       </c>
       <c r="I2">
-        <v>0.1101774042950514</v>
+        <v>0.0557711657323559</v>
       </c>
       <c r="J2">
-        <v>0.09330026852322497</v>
+        <v>0.04459327567571193</v>
       </c>
       <c r="K2">
-        <v>108</v>
+        <v>75.7</v>
       </c>
       <c r="L2">
-        <v>0.09167303284950344</v>
+        <v>0.05440563461262038</v>
       </c>
       <c r="M2">
-        <v>82.5</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.09851922617625986</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.7638888888888888</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>82.5</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.09851922617625986</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.7638888888888888</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>117.4</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.140195844279914</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0.1038062283737024</v>
+        <v>0.1075436851825543</v>
       </c>
       <c r="X2">
-        <v>0.0904165081449806</v>
+        <v>0.08092284750012169</v>
       </c>
       <c r="Y2">
-        <v>0.01338972022872181</v>
+        <v>0.02662083768243266</v>
       </c>
       <c r="Z2">
-        <v>1.184734513274336</v>
+        <v>2.157543805241123</v>
       </c>
       <c r="AA2">
-        <v>0.1105360482172278</v>
+        <v>0.0962119456895419</v>
       </c>
       <c r="AB2">
-        <v>0.08779430083044153</v>
+        <v>0.07840346149100932</v>
       </c>
       <c r="AC2">
-        <v>0.02274174738678625</v>
+        <v>0.01780848419853258</v>
       </c>
       <c r="AD2">
-        <v>58.4</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>58.4</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>-59.00000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.06519312346505916</v>
+        <v>0.07440823691752467</v>
       </c>
       <c r="AI2">
-        <v>0.07625016320668494</v>
+        <v>0.07180170029703983</v>
       </c>
       <c r="AJ2">
-        <v>-0.07579650565262078</v>
+        <v>0.07440823691752467</v>
       </c>
       <c r="AK2">
-        <v>-0.0909791827293755</v>
+        <v>0.07180170029703983</v>
       </c>
       <c r="AL2">
-        <v>2.59</v>
+        <v>2.84</v>
       </c>
       <c r="AM2">
-        <v>2.59</v>
+        <v>2.84</v>
       </c>
       <c r="AN2">
-        <v>0.3847167325428195</v>
+        <v>0.7024048096192385</v>
       </c>
       <c r="AO2">
-        <v>50.11583011583012</v>
+        <v>27.32394366197183</v>
       </c>
       <c r="AP2">
-        <v>-0.38866930171278</v>
+        <v>0.7024048096192385</v>
       </c>
       <c r="AQ2">
-        <v>50.11583011583012</v>
+        <v>27.32394366197183</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0272</v>
+        <v>0.0405</v>
       </c>
       <c r="E3">
-        <v>0.0634</v>
+        <v>-0.0119</v>
       </c>
       <c r="G3">
-        <v>0.1499023851965028</v>
+        <v>0.1167169757079201</v>
       </c>
       <c r="H3">
-        <v>0.1499023851965028</v>
+        <v>0.1167169757079201</v>
       </c>
       <c r="I3">
-        <v>0.1101774042950514</v>
+        <v>0.0557711657323559</v>
       </c>
       <c r="J3">
-        <v>0.09330026852322497</v>
+        <v>0.04459327567571193</v>
       </c>
       <c r="K3">
-        <v>108</v>
+        <v>75.7</v>
       </c>
       <c r="L3">
-        <v>0.09167303284950344</v>
+        <v>0.05440563461262038</v>
       </c>
       <c r="M3">
-        <v>82.5</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.09851922617625986</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.7638888888888888</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>82.5</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.09851922617625986</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.7638888888888888</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>117.4</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.140195844279914</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1038062283737024</v>
+        <v>0.1075436851825543</v>
       </c>
       <c r="X3">
-        <v>0.0904165081449806</v>
+        <v>0.08092284750012169</v>
       </c>
       <c r="Y3">
-        <v>0.01338972022872181</v>
+        <v>0.02662083768243266</v>
       </c>
       <c r="Z3">
-        <v>1.184734513274336</v>
+        <v>2.157543805241123</v>
       </c>
       <c r="AA3">
-        <v>0.1105360482172278</v>
+        <v>0.0962119456895419</v>
       </c>
       <c r="AB3">
-        <v>0.08779430083044153</v>
+        <v>0.07840346149100932</v>
       </c>
       <c r="AC3">
-        <v>0.02274174738678625</v>
+        <v>0.01780848419853258</v>
       </c>
       <c r="AD3">
-        <v>58.4</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>58.4</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>-59.00000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.06519312346505916</v>
+        <v>0.07440823691752467</v>
       </c>
       <c r="AI3">
-        <v>0.07625016320668494</v>
+        <v>0.07180170029703983</v>
       </c>
       <c r="AJ3">
-        <v>-0.07579650565262078</v>
+        <v>0.07440823691752467</v>
       </c>
       <c r="AK3">
-        <v>-0.0909791827293755</v>
+        <v>0.07180170029703983</v>
       </c>
       <c r="AL3">
-        <v>2.59</v>
+        <v>2.84</v>
       </c>
       <c r="AM3">
-        <v>2.59</v>
+        <v>2.84</v>
       </c>
       <c r="AN3">
-        <v>0.3847167325428195</v>
+        <v>0.7024048096192385</v>
       </c>
       <c r="AO3">
-        <v>50.11583011583012</v>
+        <v>27.32394366197183</v>
       </c>
       <c r="AP3">
-        <v>-0.38866930171278</v>
+        <v>0.7024048096192385</v>
       </c>
       <c r="AQ3">
-        <v>50.11583011583012</v>
+        <v>27.32394366197183</v>
       </c>
     </row>
   </sheetData>
